--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:35:49+00:00</t>
+    <t>2026-03-10T12:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:49:22+00:00</t>
+    <t>2026-03-10T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T15:33:20+00:00</t>
+    <t>2026-03-18T15:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,10 +463,10 @@
 </t>
   </si>
   <si>
-    <t>Unik identifikator(er) for episoden, som brukes ved rapportering til NPR</t>
-  </si>
-  <si>
-    <t>En eller flere unike identifikatorer (string og/eller UUID) som identifiserer episoden entydig i helseinstitusjonens systemer. Brukes ved rapportering til Norsk pasientregister (NPR). Kan inneholde både string-basert og UUID-basert identifikator samtidig.</t>
+    <t>NPR episodeidentifikator som sendes til LMDI</t>
+  </si>
+  <si>
+    <t>Unik identifikator for episoden som skal sendes til LMDI. Selv om avsender kan ha flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til LMDI. Dersom flere identifiere finnes, velges gjerne den første eller foretrukne identifikatoren lokalt. Den valgte identifikatoren skal oppgis med sin string-representasjon og/eller UUID-representasjon dersom begge er tilgjengelig.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:12+00:00</t>
+    <t>2026-04-21T11:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,10 +463,10 @@
 </t>
   </si>
   <si>
-    <t>NPR episodeidentifikator som sendes til LMDI</t>
-  </si>
-  <si>
-    <t>Unik identifikator for episoden som skal sendes til LMDI. Selv om avsender kan ha flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til LMDI. Dersom flere identifiere finnes, velges gjerne den første eller foretrukne identifikatoren lokalt. Den valgte identifikatoren skal oppgis med sin string-representasjon og/eller UUID-representasjon dersom begge er tilgjengelig.</t>
+    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR).</t>
+  </si>
+  <si>
+    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Hvis det er registrert flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til Legemiddelregisteret (LMR). Velg enten den første eller den lokalt foretrukne identifikatoren. Den valgte identifikatoren skal oppgis med sin string-representasjon og/eller UUID-representasjon, dersom begge er tilgjengelige oppgis begge.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:26:56+00:00</t>
+    <t>2026-05-11T08:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:19:23+00:00</t>
+    <t>2026-05-31T19:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil for en behandlingsepisode basert på Encounter-ressursen i FHIR. Denne profilen representerer et klinisk møte eller en behandling i helsevesenet, med fokus på organisatorisk tilhørighet.</t>
+    <t>En behandlingsepisode som representerer et klinisk møte, konsultasjon, innleggelse eller en behandling i helsevesenet, med fokus på organisatorisk tilhørighet.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-31T19:08:08+00:00</t>
+    <t>2026-06-12T10:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -466,7 +466,7 @@
     <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR).</t>
   </si>
   <si>
-    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Hvis det er registrert flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til Legemiddelregisteret (LMR). Velg enten den første eller den lokalt foretrukne identifikatoren. Den valgte identifikatoren skal oppgis med sin string-representasjon og/eller UUID-representasjon, dersom begge er tilgjengelige oppgis begge.</t>
+    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Identifikatoren skal oppgis med sin string-representasjon og/eller UUID-representasjon, dersom begge er tilgjengelige oppgis begge.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -2898,7 +2898,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>89</v>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:49:58+00:00</t>
+    <t>2026-08-24T07:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
